--- a/Client/Configs/GameConfig/Datas/skill_level.xlsx
+++ b/Client/Configs/GameConfig/Datas/skill_level.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,16 @@
           <t>fallbackColor</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>resourceCost</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>resourceGain</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +519,16 @@
           <t>string</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -556,6 +576,16 @@
           <t>c</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -603,117 +633,1035 @@
           <t>Fallback color.</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Resource cost.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Resource gain on successful cast/impact.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>100101</v>
+        <v>110101</v>
       </c>
       <c r="C5" t="n">
-        <v>1001</v>
+        <v>1101</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>300101</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.45</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>#40C7FFFF</t>
-        </is>
+          <t>#FFFFFFFF</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>100201</v>
+        <v>110102</v>
       </c>
       <c r="C6" t="n">
-        <v>1002</v>
+        <v>1101</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>300102</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.75</v>
+        <v>0.9</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>1.8</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>#FF6114FF</t>
-        </is>
+          <t>#FFFFFFFF</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>100301</v>
+        <v>110103</v>
       </c>
       <c r="C7" t="n">
-        <v>1003</v>
+        <v>1101</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>#66FFAAFF</t>
-        </is>
+          <t>#FFFFFFFF</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>100401</v>
+        <v>110201</v>
       </c>
       <c r="C8" t="n">
-        <v>1004</v>
+        <v>1102</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>300202</v>
       </c>
       <c r="F8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>#FFD36BFF</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>110202</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1102</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>300202</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#FFD36BFF</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>110203</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1102</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>300202</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>#FFD36BFF</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>110301</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>300203</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#FFD36BFF</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>20</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>110302</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>300203</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>#FFD36BFF</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>22</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>110303</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>300203</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>#FFD36BFF</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>24</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>120101</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1201</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>300301</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>#B388FFFF</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>120102</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1201</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>300301</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#B388FFFF</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>120103</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1201</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>300301</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>14</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>#B388FFFF</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>120201</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>300101</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>#40C7FFFF</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>15</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>120202</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>300101</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>#40C7FFFF</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>17</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>120203</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>300101</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>13</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>#40C7FFFF</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>19</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>120301</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>300102</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>#FF6114FF</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>20</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>120302</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>300102</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>#FF6114FF</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>23</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>120303</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>300102</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>11</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>#FF6114FF</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>26</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>130101</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1301</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>300401</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>#FFECA3FF</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>130102</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1301</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>300401</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>#FFECA3FF</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>130103</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1301</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>300401</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>13</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>#FFECA3FF</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>130201</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>300402</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>#66FFAAFF</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>10</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>130202</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>300402</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>#66FFAAFF</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>130203</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>300402</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>#66FFAAFF</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>13</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>130301</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1303</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>300403</v>
+      </c>
+      <c r="F29" t="n">
+        <v>30</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>#F8F2D8FF</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>60</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>130302</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1303</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>300403</v>
+      </c>
+      <c r="F30" t="n">
+        <v>28</v>
+      </c>
+      <c r="G30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>#F8F2D8FF</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>65</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>130303</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1303</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>300403</v>
+      </c>
+      <c r="F31" t="n">
+        <v>26</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#F8F2D8FF</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>70</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>100401</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G32" t="n">
         <v>4</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>#FFD86BFF</t>
         </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>100402</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>#FFD86BFF</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>100403</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>#FFD86BFF</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
